--- a/excels/Libro1.xlsx
+++ b/excels/Libro1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://conasamigobmx-my.sharepoint.com/personal/hector_soto_conasami_gob_mx/Documents/Escritorio/Negociación laboral/excels/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://conasamigobmx-my.sharepoint.com/personal/hector_soto_conasami_gob_mx/Documents/Escritorio/CAEL/Informes/Negociación laboral/excels/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="102" documentId="8_{14B7470B-4785-4325-A91E-26A86C032CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13037466-A368-45FA-B5CD-18BD05024ECA}"/>
+  <xr:revisionPtr revIDLastSave="109" documentId="8_{14B7470B-4785-4325-A91E-26A86C032CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63A70095-75C8-4CC0-9DEC-D6E7DBD45F47}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{DDB61E64-FF81-4AC5-AB1D-54D719AFA3B5}"/>
+    <workbookView xWindow="-28920" yWindow="465" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{DDB61E64-FF81-4AC5-AB1D-54D719AFA3B5}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="89">
   <si>
     <t>HUELGAS VIGENTES EN LA JURISDICCIÓN FEDERAL</t>
   </si>
@@ -333,6 +333,9 @@
   </si>
   <si>
     <t>Reparto de utilidades</t>
+  </si>
+  <si>
+    <t>Otras</t>
   </si>
 </sst>
 </file>
@@ -523,6 +526,15 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -531,14 +543,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -547,21 +565,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -582,7 +585,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -899,21 +902,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F009B841-0D57-4DA2-949E-60C0F315EDB3}">
   <dimension ref="B2:I38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:9" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B2" s="21" t="s">
+    <row r="2" spans="2:9" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-    </row>
-    <row r="3" spans="2:9" ht="51" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+    </row>
+    <row r="3" spans="2:9" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
@@ -939,7 +942,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="2:9" ht="219.75" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:9" ht="190.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
         <v>80</v>
       </c>
@@ -965,46 +968,46 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="84.4" x14ac:dyDescent="0.45">
-      <c r="B5" s="15" t="s">
+    <row r="5" spans="2:9" ht="86.25" x14ac:dyDescent="0.25">
+      <c r="B5" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="27" t="s">
         <v>84</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="21">
         <v>45723</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="18">
+      <c r="I5" s="15">
         <v>130</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="118.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B6" s="17"/>
-      <c r="C6" s="23"/>
+    <row r="6" spans="2:9" ht="121.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="20"/>
+      <c r="C6" s="28"/>
       <c r="D6" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="E6" s="20"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="20"/>
-    </row>
-    <row r="7" spans="2:9" ht="50.65" x14ac:dyDescent="0.45">
-      <c r="B7" s="15" t="s">
+      <c r="E6" s="17"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="17"/>
+    </row>
+    <row r="7" spans="2:9" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="B7" s="18" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="5" t="s">
@@ -1013,127 +1016,127 @@
       <c r="D7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="21">
         <v>45642</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="H7" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="I7" s="18">
+      <c r="I7" s="15">
         <v>133</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="33.75" x14ac:dyDescent="0.45">
-      <c r="B8" s="16"/>
+    <row r="8" spans="2:9" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="B8" s="19"/>
       <c r="C8" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="19"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="19"/>
-    </row>
-    <row r="9" spans="2:9" ht="33.75" x14ac:dyDescent="0.45">
-      <c r="B9" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="16"/>
+    </row>
+    <row r="9" spans="2:9" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="B9" s="19"/>
       <c r="C9" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="19"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="19"/>
-    </row>
-    <row r="10" spans="2:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B10" s="17"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="16"/>
+    </row>
+    <row r="10" spans="2:9" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="20"/>
       <c r="C10" s="6"/>
       <c r="D10" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="20"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="20"/>
-    </row>
-    <row r="11" spans="2:9" ht="50.65" x14ac:dyDescent="0.45">
+      <c r="E10" s="17"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="17"/>
+    </row>
+    <row r="11" spans="2:9" ht="34.5" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="18" t="s">
         <v>22</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="G11" s="24">
+      <c r="G11" s="21">
         <v>45636</v>
       </c>
-      <c r="H11" s="15" t="s">
+      <c r="H11" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="I11" s="18">
+      <c r="I11" s="15">
         <v>125</v>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="33.75" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:9" ht="34.5" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="16"/>
+      <c r="C12" s="19"/>
       <c r="D12" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="19"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="19"/>
-    </row>
-    <row r="13" spans="2:9" ht="33.75" x14ac:dyDescent="0.45">
+      <c r="E12" s="16"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="16"/>
+    </row>
+    <row r="13" spans="2:9" ht="34.5" x14ac:dyDescent="0.25">
       <c r="B13" s="4"/>
-      <c r="C13" s="16"/>
+      <c r="C13" s="19"/>
       <c r="D13" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="19"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="19"/>
-    </row>
-    <row r="14" spans="2:9" ht="84.75" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="E13" s="16"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="16"/>
+    </row>
+    <row r="14" spans="2:9" ht="87" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="3"/>
-      <c r="C14" s="17"/>
+      <c r="C14" s="20"/>
       <c r="D14" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="20"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="20"/>
-    </row>
-    <row r="15" spans="2:9" ht="50.65" x14ac:dyDescent="0.45">
+      <c r="E14" s="17"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="17"/>
+    </row>
+    <row r="15" spans="2:9" ht="34.5" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
         <v>29</v>
       </c>
@@ -1143,23 +1146,23 @@
       <c r="D15" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E15" s="18" t="s">
+      <c r="E15" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="15" t="s">
+      <c r="F15" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="G15" s="24">
+      <c r="G15" s="21">
         <v>45569</v>
       </c>
-      <c r="H15" s="15" t="s">
+      <c r="H15" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="I15" s="18">
+      <c r="I15" s="15">
         <v>118</v>
       </c>
     </row>
-    <row r="16" spans="2:9" ht="50.65" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:9" ht="51.75" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
         <v>30</v>
       </c>
@@ -1169,25 +1172,25 @@
       <c r="D16" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E16" s="19"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="19"/>
-    </row>
-    <row r="17" spans="2:9" ht="101.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="E16" s="16"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="16"/>
+    </row>
+    <row r="17" spans="2:9" ht="104.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="3"/>
       <c r="C17" s="7"/>
       <c r="D17" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E17" s="20"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="20"/>
-    </row>
-    <row r="18" spans="2:9" ht="219.75" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="E17" s="17"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="17"/>
+    </row>
+    <row r="18" spans="2:9" ht="190.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="8" t="s">
         <v>36</v>
       </c>
@@ -1213,7 +1216,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="152.25" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="19" spans="2:9" ht="156" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="8" t="s">
         <v>41</v>
       </c>
@@ -1239,7 +1242,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="2:9" ht="152.25" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="20" spans="2:9" ht="156" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="8" t="s">
         <v>41</v>
       </c>
@@ -1265,69 +1268,69 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="2:9" ht="185.65" x14ac:dyDescent="0.45">
-      <c r="B21" s="15" t="s">
+    <row r="21" spans="2:9" ht="172.5" x14ac:dyDescent="0.25">
+      <c r="B21" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="18" t="s">
         <v>47</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E21" s="18" t="s">
+      <c r="E21" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F21" s="15" t="s">
+      <c r="F21" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="G21" s="24">
+      <c r="G21" s="21">
         <v>45488</v>
       </c>
-      <c r="H21" s="15" t="s">
+      <c r="H21" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="I21" s="18">
+      <c r="I21" s="15">
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="2:9" ht="67.5" x14ac:dyDescent="0.45">
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
+    <row r="22" spans="2:9" ht="51.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
       <c r="D22" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E22" s="19"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="19"/>
-    </row>
-    <row r="23" spans="2:9" ht="50.65" x14ac:dyDescent="0.45">
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="16"/>
+    </row>
+    <row r="23" spans="2:9" ht="51.75" x14ac:dyDescent="0.25">
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
       <c r="D23" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E23" s="19"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="19"/>
-    </row>
-    <row r="24" spans="2:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="16"/>
+    </row>
+    <row r="24" spans="2:9" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
       <c r="D24" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E24" s="20"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="20"/>
-    </row>
-    <row r="25" spans="2:9" ht="219.75" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="E24" s="17"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="17"/>
+    </row>
+    <row r="25" spans="2:9" ht="190.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="8" t="s">
         <v>53</v>
       </c>
@@ -1353,7 +1356,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="26" spans="2:9" ht="152.25" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="26" spans="2:9" ht="156" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="8" t="s">
         <v>56</v>
       </c>
@@ -1379,7 +1382,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="2:9" ht="152.25" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="27" spans="2:9" ht="156" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="8" t="s">
         <v>56</v>
       </c>
@@ -1405,7 +1408,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="2:9" ht="219.75" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="28" spans="2:9" ht="190.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="8" t="s">
         <v>58</v>
       </c>
@@ -1431,7 +1434,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="2:9" ht="169.15" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="29" spans="2:9" ht="156" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="8" t="s">
         <v>56</v>
       </c>
@@ -1457,7 +1460,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="2:9" ht="186" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="30" spans="2:9" ht="173.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="8" t="s">
         <v>58</v>
       </c>
@@ -1483,7 +1486,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="31" spans="2:9" ht="354.75" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="31" spans="2:9" ht="328.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="8" t="s">
         <v>56</v>
       </c>
@@ -1509,7 +1512,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="32" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="8" t="s">
         <v>56</v>
       </c>
@@ -1535,7 +1538,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="33" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="33" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="8" t="s">
         <v>72</v>
       </c>
@@ -1561,89 +1564,68 @@
         <v>403</v>
       </c>
     </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.45">
-      <c r="B34" s="28" t="s">
+    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B34" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="28"/>
-      <c r="H34" s="28"/>
-      <c r="I34" s="28"/>
-    </row>
-    <row r="35" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B35" s="27" t="s">
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="25"/>
+    </row>
+    <row r="35" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="C35" s="27"/>
-      <c r="D35" s="27"/>
-      <c r="E35" s="27"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="27"/>
-      <c r="H35" s="27"/>
-      <c r="I35" s="27"/>
-    </row>
-    <row r="36" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B36" s="27" t="s">
+      <c r="C35" s="24"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="24"/>
+      <c r="H35" s="24"/>
+      <c r="I35" s="24"/>
+    </row>
+    <row r="36" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="C36" s="27"/>
-      <c r="D36" s="27"/>
-      <c r="E36" s="27"/>
-      <c r="F36" s="27"/>
-      <c r="G36" s="27"/>
-      <c r="H36" s="27"/>
-      <c r="I36" s="27"/>
-    </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.45">
-      <c r="B37" s="27" t="s">
+      <c r="C36" s="24"/>
+      <c r="D36" s="24"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="24"/>
+      <c r="H36" s="24"/>
+      <c r="I36" s="24"/>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B37" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="C37" s="27"/>
-      <c r="D37" s="27"/>
-      <c r="E37" s="27"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="27"/>
-      <c r="I37" s="27"/>
-    </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.45">
-      <c r="B38" s="27" t="s">
+      <c r="C37" s="24"/>
+      <c r="D37" s="24"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="24"/>
+      <c r="H37" s="24"/>
+      <c r="I37" s="24"/>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B38" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="C38" s="27"/>
-      <c r="D38" s="27"/>
-      <c r="E38" s="27"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
-      <c r="H38" s="27"/>
-      <c r="I38" s="27"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="24"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="24"/>
+      <c r="H38" s="24"/>
+      <c r="I38" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="E21:E24"/>
-    <mergeCell ref="F21:F24"/>
-    <mergeCell ref="G21:G24"/>
-    <mergeCell ref="H21:H24"/>
-    <mergeCell ref="I21:I24"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="G15:G17"/>
-    <mergeCell ref="H15:H17"/>
-    <mergeCell ref="I15:I17"/>
-    <mergeCell ref="I7:I10"/>
-    <mergeCell ref="C11:C14"/>
-    <mergeCell ref="E11:E14"/>
-    <mergeCell ref="F11:F14"/>
-    <mergeCell ref="G11:G14"/>
-    <mergeCell ref="H11:H14"/>
-    <mergeCell ref="B36:I36"/>
-    <mergeCell ref="B37:I37"/>
-    <mergeCell ref="B38:I38"/>
-    <mergeCell ref="B34:I34"/>
-    <mergeCell ref="B35:I35"/>
     <mergeCell ref="B21:B24"/>
     <mergeCell ref="C21:C24"/>
     <mergeCell ref="I11:I14"/>
@@ -1660,6 +1642,27 @@
     <mergeCell ref="F7:F10"/>
     <mergeCell ref="G7:G10"/>
     <mergeCell ref="H7:H10"/>
+    <mergeCell ref="B36:I36"/>
+    <mergeCell ref="B37:I37"/>
+    <mergeCell ref="B38:I38"/>
+    <mergeCell ref="B34:I34"/>
+    <mergeCell ref="B35:I35"/>
+    <mergeCell ref="I7:I10"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="E11:E14"/>
+    <mergeCell ref="F11:F14"/>
+    <mergeCell ref="G11:G14"/>
+    <mergeCell ref="H11:H14"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="G15:G17"/>
+    <mergeCell ref="H15:H17"/>
+    <mergeCell ref="I15:I17"/>
+    <mergeCell ref="E21:E24"/>
+    <mergeCell ref="F21:F24"/>
+    <mergeCell ref="G21:G24"/>
+    <mergeCell ref="H21:H24"/>
+    <mergeCell ref="I21:I24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1667,13 +1670,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0E6A4B2-D31F-450E-B226-BD397D1921B1}">
-  <dimension ref="A1:C33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:C34"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="11.3984375" style="14"/>
+    <col min="3" max="3" width="11.42578125" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="34.15" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:3" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
@@ -1684,20 +1687,20 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="34.15" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:3" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="10">
+        <v>46055</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="10">
         <v>45864</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="34.15" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A3" s="10">
-        <v>45865</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>27</v>
@@ -1706,131 +1709,131 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="34.15" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:3" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10">
-        <v>45866</v>
+        <v>45865</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>27</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="10">
+        <v>45866</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A5" s="10">
+    <row r="6" spans="1:3" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="10">
         <v>45777</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B6" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C6" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="24">
+    <row r="7" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="21">
         <v>45723</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B7" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C7" s="18" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="25"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="17"/>
-    </row>
-    <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="24">
+    <row r="8" spans="1:3" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="23"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="20"/>
+    </row>
+    <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="21">
         <v>45642</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B9" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C9" s="18" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="26"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="16"/>
-    </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="26"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="16"/>
-    </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="25"/>
-      <c r="B11" s="20"/>
-      <c r="C11" s="17"/>
-    </row>
-    <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="24">
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="22"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="19"/>
+    </row>
+    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="22"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="19"/>
+    </row>
+    <row r="12" spans="1:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="23"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="20"/>
+    </row>
+    <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="21">
         <v>45636</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B13" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C13" s="18" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="26"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="16"/>
-    </row>
-    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="26"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="16"/>
-    </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A15" s="25"/>
-      <c r="B15" s="20"/>
-      <c r="C15" s="17"/>
-    </row>
-    <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="24">
+    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="22"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="19"/>
+    </row>
+    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="22"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="19"/>
+    </row>
+    <row r="16" spans="1:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="23"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="20"/>
+    </row>
+    <row r="17" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="21">
         <v>45569</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B17" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C17" s="18" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="26"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="16"/>
-    </row>
-    <row r="18" spans="1:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A18" s="25"/>
-      <c r="B18" s="20"/>
-      <c r="C18" s="17"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A19" s="10">
+    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="22"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="19"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="23"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="20"/>
+    </row>
+    <row r="20" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="10">
         <v>45534</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="34.15" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A20" s="10">
-        <v>45513</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>39</v>
@@ -1839,7 +1842,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="34.15" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:3" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="10">
         <v>45513</v>
       </c>
@@ -1847,58 +1850,58 @@
         <v>39</v>
       </c>
       <c r="C21" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="10">
+        <v>45513</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="6" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="24">
+    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="21">
         <v>45488</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B23" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C23" s="18" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="26"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="16"/>
-    </row>
-    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="26"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="16"/>
-    </row>
-    <row r="25" spans="1:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A25" s="25"/>
-      <c r="B25" s="20"/>
-      <c r="C25" s="17"/>
-    </row>
-    <row r="26" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A26" s="10">
+    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="22"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="19"/>
+    </row>
+    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="22"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="19"/>
+    </row>
+    <row r="26" spans="1:3" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="23"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="20"/>
+    </row>
+    <row r="27" spans="1:3" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="10">
         <v>45470</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="34.15" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A27" s="10">
-        <v>45351</v>
       </c>
       <c r="B27" s="9" t="s">
         <v>39</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="34.15" thickBot="1" x14ac:dyDescent="0.5">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>45351</v>
       </c>
@@ -1909,78 +1912,89 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="34.15" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:3" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
-        <v>45268</v>
+        <v>45267</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>39</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="34.15" thickBot="1" x14ac:dyDescent="0.5">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
-        <v>45262</v>
+        <v>45268</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="34.15" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:3" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
-        <v>45191</v>
+        <v>45262</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="34.15" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:3" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
-        <v>44973</v>
+        <v>45191</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>39</v>
       </c>
       <c r="C32" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="10">
+        <v>44973</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="6" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="34.15" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A33" s="10">
+    <row r="34" spans="1:3" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="10">
         <v>39293</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B34" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C34" s="6" t="s">
         <v>28</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C22:C25"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B12:B15"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="C12:C15"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C8:C11"/>
-    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="C23:C26"/>
+    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="B23:B26"/>
+    <mergeCell ref="C13:C16"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="A9:A12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
